--- a/tests/test_data/pvacseq_create_peptide_ordering_form/expected_output.Colored_Peptides.xlsx
+++ b/tests/test_data/pvacseq_create_peptide_ordering_form/expected_output.Colored_Peptides.xlsx
@@ -34,12 +34,12 @@
     <t>Comments</t>
   </si>
   <si>
+    <t>Best Peptide Class I</t>
+  </si>
+  <si>
     <t>51mer ID</t>
   </si>
   <si>
-    <t>Best Peptide Class I</t>
-  </si>
-  <si>
     <t>Pos</t>
   </si>
   <si>
@@ -338,7 +338,6 @@
     <r>
       <rPr>
         <b/>
-        <u/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
@@ -606,12 +605,12 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>KFNPQTDYL</t>
+  </si>
+  <si>
     <t>ACO2.ENST00000216254.4.510E/Q</t>
   </si>
   <si>
-    <t>KFNPQTDYL</t>
-  </si>
-  <si>
     <t>E510Q</t>
   </si>
   <si>
@@ -888,7 +887,6 @@
     <r>
       <rPr>
         <b/>
-        <u/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
@@ -1154,12 +1152,12 @@
     </r>
   </si>
   <si>
+    <t>LYYSYGLLHI</t>
+  </si>
+  <si>
     <t>PKDREJ.ENST00000253255.5.1875T/I</t>
   </si>
   <si>
-    <t>LYYSYGLLHI</t>
-  </si>
-  <si>
     <t>T1875I</t>
   </si>
   <si>
@@ -1420,7 +1418,6 @@
     </r>
     <r>
       <rPr>
-        <u/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
@@ -1684,12 +1681,12 @@
     <t>HLA-E*01:01</t>
   </si>
   <si>
+    <t>ARPPQQPVP</t>
+  </si>
+  <si>
     <t>GGA1.ENST00000343632.4.484P/A</t>
   </si>
   <si>
-    <t>ARPPQQPVP</t>
-  </si>
-  <si>
     <t>P484A</t>
   </si>
   <si>
@@ -1950,7 +1947,6 @@
     </r>
     <r>
       <rPr>
-        <u/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
@@ -2211,12 +2207,12 @@
     </r>
   </si>
   <si>
+    <t>YQPCDDMDY</t>
+  </si>
+  <si>
     <t>CACNA1I.ENST00000402142.3.107C/Y</t>
   </si>
   <si>
-    <t>YQPCDDMDY</t>
-  </si>
-  <si>
     <t>C107Y</t>
   </si>
   <si>
@@ -2233,6 +2229,16 @@
   </si>
   <si>
     <r>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>G</t>
     </r>
     <r>
@@ -2494,7 +2500,6 @@
     <r>
       <rPr>
         <b/>
-        <u/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
@@ -2741,6 +2746,45 @@
       </rPr>
       <t>N</t>
     </r>
+  </si>
+  <si>
+    <t>HLA-E*01:01/HLA-DRB1*11:01</t>
+  </si>
+  <si>
+    <t>ATLSRTLLL</t>
+  </si>
+  <si>
+    <t>PRICKLE4.ENST00000458694.1.287-288-/L</t>
+  </si>
+  <si>
+    <t>-287-288L</t>
+  </si>
+  <si>
+    <t>ENST00000458694.1</t>
+  </si>
+  <si>
+    <t>LSRTLLLAAAGGSSL</t>
+  </si>
+  <si>
+    <t>MT.5.CECR2.ENST00000262608.8.missense.535R/H</t>
+  </si>
+  <si>
+    <t>H_NJ-HCC1395-HCC1395.MT.5.CECR2</t>
+  </si>
+  <si>
+    <r>
+      <t>W</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2759,35 +2803,1483 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>W</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>P</t>
     </r>
-  </si>
-  <si>
-    <t>HLA-E*01:01/HLA-DRB1*11:01</t>
-  </si>
-  <si>
-    <t>PRICKLE4.ENST00000458694.1.287-288-/L</t>
-  </si>
-  <si>
-    <t>ATLSRTLLL</t>
-  </si>
-  <si>
-    <t>-287-288L</t>
-  </si>
-  <si>
-    <t>ENST00000458694.1</t>
-  </si>
-  <si>
-    <t>LSRTLLLAAAGGSSL</t>
-  </si>
-  <si>
-    <t>MT.5.CECR2.ENST00000262608.8.missense.535R/H</t>
-  </si>
-  <si>
-    <t>H_NJ-HCC1395-HCC1395.MT.5.CECR2</t>
-  </si>
-  <si>
-    <r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+  </si>
+  <si>
+    <t>WTHSRDPEG</t>
+  </si>
+  <si>
+    <t>CECR2.ENST00000262608.8.535R/H</t>
+  </si>
+  <si>
+    <t>R535H</t>
+  </si>
+  <si>
+    <t>ENST00000262608.8</t>
+  </si>
+  <si>
+    <t>GGSHVWTHSRDPEGS</t>
+  </si>
+  <si>
+    <t>MT.1.IGFBP2.ENST00000233809.4.inframe_ins.20L/LLP</t>
+  </si>
+  <si>
+    <t>H_NJ-HCC1395-HCC1395.MT.1.IGFBP2</t>
+  </si>
+  <si>
+    <r>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+  </si>
+  <si>
+    <t>LLPLLPLLL</t>
+  </si>
+  <si>
+    <t>IGFBP2.ENST00000233809.4.20L/LLP</t>
+  </si>
+  <si>
+    <t>L20LLP</t>
+  </si>
+  <si>
+    <t>ENST00000233809.4</t>
+  </si>
+  <si>
+    <t>LPLLPLLLLLGASGG</t>
+  </si>
+  <si>
+    <t>MT.6.USP18.ENST00000215794.7.missense.124A/V</t>
+  </si>
+  <si>
+    <t>H_NJ-HCC1395-HCC1395.MT.6.USP18</t>
+  </si>
+  <si>
+    <r>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>W</t>
     </r>
     <r>
@@ -2798,6 +4290,152 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>N</t>
+    </r>
+  </si>
+  <si>
+    <t>LVYCLQKCN</t>
+  </si>
+  <si>
+    <t>USP18.ENST00000215794.7.124A/V</t>
+  </si>
+  <si>
+    <t>A124V</t>
+  </si>
+  <si>
+    <t>ENST00000215794.7</t>
+  </si>
+  <si>
+    <t>ELVYCLQKCNVPLFV</t>
+  </si>
+  <si>
+    <t>MT.22.PANX2.ENST00000395842.2.missense.147S/F</t>
+  </si>
+  <si>
+    <t>H_NJ-HCC1395-HCC1395.MT.22.PANX2</t>
+  </si>
+  <si>
+    <r>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>I</t>
     </r>
     <r>
@@ -2808,10 +4446,193 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>W</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>R</t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
@@ -2822,6 +4643,88 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
@@ -2838,6 +4741,76 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>E</t>
     </r>
     <r>
@@ -2848,6 +4821,512 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+  </si>
+  <si>
+    <t>FLAFTRLTS</t>
+  </si>
+  <si>
+    <t>PANX2.ENST00000395842.2.147S/F</t>
+  </si>
+  <si>
+    <t>S147F</t>
+  </si>
+  <si>
+    <t>ENST00000395842.2</t>
+  </si>
+  <si>
+    <t>GWEFLAFTRLTSELN</t>
+  </si>
+  <si>
+    <t>MT.13.ELFN2.ENST00000402918.2.missense.186P/L</t>
+  </si>
+  <si>
+    <t>H_NJ-HCC1395-HCC1395.MT.13.ELFN2</t>
+  </si>
+  <si>
+    <r>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>W</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>K</t>
     </r>
     <r>
@@ -2858,6 +5337,62 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+  </si>
+  <si>
+    <t>MVCELAGNL</t>
+  </si>
+  <si>
+    <t>ELFN2.ENST00000402918.2.186P/L</t>
+  </si>
+  <si>
+    <t>P186L</t>
+  </si>
+  <si>
+    <t>ENST00000402918.2</t>
+  </si>
+  <si>
+    <t>ASLASLMVCELAGNL</t>
+  </si>
+  <si>
+    <t>MT.14.LGALS2.ENST00000215886.4.missense.132E/Q</t>
+  </si>
+  <si>
+    <t>H_NJ-HCC1395-HCC1395.MT.14.LGALS2</t>
+  </si>
+  <si>
+    <r>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>R</t>
     </r>
     <r>
@@ -2868,10 +5403,212 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
@@ -2882,257 +5619,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>W</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
@@ -3143,6 +5641,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
@@ -3151,2868 +5650,12 @@
       </rPr>
       <t>Q</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Q</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-  </si>
-  <si>
-    <t>CECR2.ENST00000262608.8.535R/H</t>
-  </si>
-  <si>
-    <t>WTHSRDPEG</t>
-  </si>
-  <si>
-    <t>R535H</t>
-  </si>
-  <si>
-    <t>ENST00000262608.8</t>
-  </si>
-  <si>
-    <t>GGSHVWTHSRDPEGS</t>
-  </si>
-  <si>
-    <t>MT.1.IGFBP2.ENST00000233809.4.inframe_ins.20L/LLP</t>
-  </si>
-  <si>
-    <t>H_NJ-HCC1395-HCC1395.MT.1.IGFBP2</t>
-  </si>
-  <si>
-    <r>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-  </si>
-  <si>
-    <t>IGFBP2.ENST00000233809.4.20L/LLP</t>
-  </si>
-  <si>
-    <t>LLPLLPLLL</t>
-  </si>
-  <si>
-    <t>L20LLP</t>
-  </si>
-  <si>
-    <t>ENST00000233809.4</t>
-  </si>
-  <si>
-    <t>LPLLPLLLLLGASGG</t>
-  </si>
-  <si>
-    <t>MT.6.USP18.ENST00000215794.7.missense.124A/V</t>
-  </si>
-  <si>
-    <t>H_NJ-HCC1395-HCC1395.MT.6.USP18</t>
-  </si>
-  <si>
-    <r>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Q</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Q</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Q</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Q</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Q</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Q</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>W</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-  </si>
-  <si>
-    <t>USP18.ENST00000215794.7.124A/V</t>
-  </si>
-  <si>
-    <t>LVYCLQKCN</t>
-  </si>
-  <si>
-    <t>A124V</t>
-  </si>
-  <si>
-    <t>ENST00000215794.7</t>
-  </si>
-  <si>
-    <t>ELVYCLQKCNVPLFV</t>
-  </si>
-  <si>
-    <t>MT.22.PANX2.ENST00000395842.2.missense.147S/F</t>
-  </si>
-  <si>
-    <t>H_NJ-HCC1395-HCC1395.MT.22.PANX2</t>
-  </si>
-  <si>
-    <r>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>W</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Q</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-  </si>
-  <si>
-    <t>PANX2.ENST00000395842.2.147S/F</t>
-  </si>
-  <si>
-    <t>FLAFTRLTS</t>
-  </si>
-  <si>
-    <t>S147F</t>
-  </si>
-  <si>
-    <t>ENST00000395842.2</t>
-  </si>
-  <si>
-    <t>GWEFLAFTRLTSELN</t>
-  </si>
-  <si>
-    <t>MT.13.ELFN2.ENST00000402918.2.missense.186P/L</t>
-  </si>
-  <si>
-    <t>H_NJ-HCC1395-HCC1395.MT.13.ELFN2</t>
-  </si>
-  <si>
-    <r>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>W</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-  </si>
-  <si>
-    <t>ELFN2.ENST00000402918.2.186P/L</t>
-  </si>
-  <si>
-    <t>MVCELAGNL</t>
-  </si>
-  <si>
-    <t>P186L</t>
-  </si>
-  <si>
-    <t>ENST00000402918.2</t>
-  </si>
-  <si>
-    <t>ASLASLMVCELAGNL</t>
-  </si>
-  <si>
-    <t>MT.14.LGALS2.ENST00000215886.4.missense.132E/Q</t>
-  </si>
-  <si>
-    <t>H_NJ-HCC1395-HCC1395.MT.14.LGALS2</t>
-  </si>
-  <si>
-    <r>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Q</t>
-    </r>
+  </si>
+  <si>
+    <t>NMSSFKLKQ</t>
   </si>
   <si>
     <t>LGALS2.ENST00000215886.4.132E/Q</t>
-  </si>
-  <si>
-    <t>NMSSFKLKQ</t>
   </si>
   <si>
     <t>E132Q</t>
@@ -6665,7 +6308,7 @@
         <v>59</v>
       </c>
       <c r="E6">
-        <v>5367.7268</v>
+        <v>5227.583500000001</v>
       </c>
       <c r="F6" t="s">
         <v>23</v>
@@ -6783,7 +6426,7 @@
         <v>42</v>
       </c>
       <c r="E8">
-        <v>5553.786</v>
+        <v>4608.668</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -7016,7 +6659,7 @@
         <v>30</v>
       </c>
       <c r="E12">
-        <v>5856.6683</v>
+        <v>2964.3629</v>
       </c>
       <c r="F12" t="s">
         <v>23</v>

--- a/tests/test_data/pvacseq_create_peptide_ordering_form/expected_output.Colored_Peptides.xlsx
+++ b/tests/test_data/pvacseq_create_peptide_ordering_form/expected_output.Colored_Peptides.xlsx
@@ -3750,6 +3750,16 @@
         <scheme val="minor"/>
       </rPr>
       <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
     </r>
   </si>
   <si>
@@ -6426,7 +6436,7 @@
         <v>42</v>
       </c>
       <c r="E8">
-        <v>4608.668</v>
+        <v>4711.810899999999</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
